--- a/BWI/bestwine_output/bestwine_Zimbabwe.xlsx
+++ b/BWI/bestwine_output/bestwine_Zimbabwe.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2148,6 +2148,208 @@
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>African Distillers Limited</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>African Distillers Limited</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>46792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Harare Province</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Lomagundi Road</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.africandistillers.co.zw</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>sales@afdis.co.zw</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>434/138/1950</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AFDISZimbabwe/</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/afdis_zw</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Butai</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>Procurement and Inventory Manager</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrick-butai-30a66a45/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>African Distillers Limited</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>African Distillers Limited</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>46792</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Harare Province</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Lomagundi Road</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.africandistillers.co.zw</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>sales@afdis.co.zw</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>434/138/1950</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AFDISZimbabwe/</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/afdis_zw</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Kamusoko</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Head of Trade (Director)</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arthur1106/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Zimbabwe.xlsx
+++ b/BWI/bestwine_output/bestwine_Zimbabwe.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2350,6 +2350,208 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>African Distillers Limited</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>African Distillers Limited</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>46792</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Harare Province</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Lomagundi Road</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.africandistillers.co.zw</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>sales@afdis.co.zw</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>434/138/1950</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AFDISZimbabwe/</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/afdis_zw</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Kamusoko</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Head of Trade (Director)</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arthur1106/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>African Distillers Limited</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>African Distillers Limited</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>46792</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Harare</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Harare Province</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Lomagundi Road</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.africandistillers.co.zw</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>sales@afdis.co.zw</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>434/138/1950</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AFDISZimbabwe/</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/afdis_zw</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Butai</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Procurement and Inventory Manager</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrick-butai-30a66a45/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
